--- a/backend/downloads/미분양주택현황보고_미분양현황_종합 (2001 ~ 2024).xlsx
+++ b/backend/downloads/미분양주택현황보고_미분양현황_종합 (2001 ~ 2024).xlsx
@@ -148,7 +148,7 @@
     <row r="2" customHeight="true" ht="25.0">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-14   10:05</t>
+          <t>다운로드 시간 : 2025-10-14   23:57</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">

--- a/backend/downloads/미분양주택현황보고_미분양현황_종합 (2001 ~ 2024).xlsx
+++ b/backend/downloads/미분양주택현황보고_미분양현황_종합 (2001 ~ 2024).xlsx
@@ -33,7 +33,7 @@
       <color indexed="8"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -52,6 +52,9 @@
       <patternFill patternType="solid">
         <fgColor rgb="C9E1F5"/>
       </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid"/>
     </fill>
   </fills>
   <borders count="6">
@@ -85,13 +88,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment vertical="center" horizontal="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment vertical="center" horizontal="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment vertical="center" horizontal="left" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment vertical="center" horizontal="left" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment vertical="center" horizontal="left" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment vertical="center" horizontal="right" wrapText="true"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -105,12 +120,10 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="71.5" customWidth="true"/>
-    <col min="2" max="2" width="42.06640625" customWidth="true"/>
-    <col min="3" max="3" width="42.06640625" customWidth="true"/>
-    <col min="4" max="4" width="42.06640625" customWidth="true"/>
-    <col min="5" max="5" width="42.06640625" customWidth="true"/>
-    <col min="6" max="6" width="84.31640625" customWidth="true"/>
+    <col min="1" max="1" width="86.84375" customWidth="true"/>
+    <col min="2" max="2" width="54.88671875" customWidth="true"/>
+    <col min="3" max="3" width="55.06640625" customWidth="true"/>
+    <col min="4" max="4" width="124.40234375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="true" ht="25.0">
@@ -134,21 +147,11 @@
           <t/>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
     </row>
     <row r="2" customHeight="true" ht="25.0">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-14   23:57</t>
+          <t>다운로드 시간 : 2025-10-15   10:05</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -162,16 +165,6 @@
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -185,7 +178,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>검색기간  : 202508 ~ 202508</t>
+          <t>검색기간  : 2024 ~ 2024</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -195,17 +188,7 @@
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>작성주기 : 매월</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>단위 : 호</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t/>
+          <t>작성주기 : 매년</t>
         </is>
       </c>
     </row>
@@ -230,46 +213,664 @@
           <t/>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
     </row>
     <row r="5" customHeight="true" ht="25.0">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>월(Monthly)</t>
+          <t>년(Annual)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>대분류</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>시군구</t>
-        </is>
-      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>부문</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>규모</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>호</t>
+          <t>미분양(12월기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" customHeight="true" ht="25.0">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>계</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>70,173</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" customHeight="true" ht="25.0">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>민간부문</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>70,173</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" customHeight="true" ht="25.0">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>공공부문</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" customHeight="true" ht="25.0">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>(준공후)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>21,480</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" customHeight="true" ht="25.0">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>전국</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>70,173</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" customHeight="true" ht="25.0">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>서울특별시</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" customHeight="true" ht="25.0">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>부산광역시</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>4,720</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" customHeight="true" ht="25.0">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>대구광역시</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>8,807</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" customHeight="true" ht="25.0">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>인천광역시</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>3,086</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" customHeight="true" ht="25.0">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>광주광역시</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>1,242</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" customHeight="true" ht="25.0">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>대전광역시</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>2,319</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" customHeight="true" ht="25.0">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>울산광역시</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>4,131</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" customHeight="true" ht="25.0">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>12,954</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" customHeight="true" ht="25.0">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>강원도</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>4,408</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" customHeight="true" ht="25.0">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>충청북도</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>2,192</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" customHeight="true" ht="25.0">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>충청남도</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>3,814</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" customHeight="true" ht="25.0">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>세종특별자치시</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" customHeight="true" ht="25.0">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>전라북도</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>2,743</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" customHeight="true" ht="25.0">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>전라남도</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>3,598</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" customHeight="true" ht="25.0">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>경상북도</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>6,987</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" customHeight="true" ht="25.0">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>경상남도</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>5,347</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" customHeight="true" ht="25.0">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>제주도</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>2,807</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" customHeight="true" ht="25.0">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>16,997</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" customHeight="true" ht="25.0">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>지방</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>53,176</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" customHeight="true" ht="25.0">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>계</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>70,173</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" customHeight="true" ht="25.0">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>40㎡이하</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>2,160</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" customHeight="true" ht="25.0">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>40-60㎡</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>7,197</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" customHeight="true" ht="25.0">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>60-85㎡</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>50,468</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" customHeight="true" ht="25.0">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>85㎡초과</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>10,348</t>
         </is>
       </c>
     </row>
@@ -278,6 +879,10 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A6:A34"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B29"/>
+    <mergeCell ref="B30:B34"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup blackAndWhite="false" orientation="portrait" paperSize="0" fitToWidth="0" fitToHeight="0"/>

--- a/backend/downloads/미분양주택현황보고_미분양현황_종합 (2001 ~ 2024).xlsx
+++ b/backend/downloads/미분양주택현황보고_미분양현황_종합 (2001 ~ 2024).xlsx
@@ -151,7 +151,7 @@
     <row r="2" customHeight="true" ht="25.0">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-15   10:05</t>
+          <t>다운로드 시간 : 2025-10-17   03:00</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -178,7 +178,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>검색기간  : 2024 ~ 2024</t>
+          <t>검색기간  : 2020 ~ 2024</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -239,7 +239,7 @@
     <row r="6" customHeight="true" ht="25.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -254,14 +254,14 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>70,173</t>
+          <t>19,005</t>
         </is>
       </c>
     </row>
     <row r="7" customHeight="true" ht="25.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -276,14 +276,14 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>70,173</t>
+          <t>19,005</t>
         </is>
       </c>
     </row>
     <row r="8" customHeight="true" ht="25.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -305,7 +305,7 @@
     <row r="9" customHeight="true" ht="25.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -320,14 +320,14 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>21,480</t>
+          <t>12,006</t>
         </is>
       </c>
     </row>
     <row r="10" customHeight="true" ht="25.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -342,14 +342,14 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>70,173</t>
+          <t>19,005</t>
         </is>
       </c>
     </row>
     <row r="11" customHeight="true" ht="25.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -364,14 +364,14 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="12" customHeight="true" ht="25.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -386,14 +386,14 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>4,720</t>
+          <t>973</t>
         </is>
       </c>
     </row>
     <row r="13" customHeight="true" ht="25.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -408,14 +408,14 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>8,807</t>
+          <t>280</t>
         </is>
       </c>
     </row>
     <row r="14" customHeight="true" ht="25.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -430,14 +430,14 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>3,086</t>
+          <t>466</t>
         </is>
       </c>
     </row>
     <row r="15" customHeight="true" ht="25.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -452,14 +452,14 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>1,242</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="16" customHeight="true" ht="25.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -474,14 +474,14 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>2,319</t>
+          <t>638</t>
         </is>
       </c>
     </row>
     <row r="17" customHeight="true" ht="25.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>4,131</t>
+          <t>468</t>
         </is>
       </c>
     </row>
     <row r="18" customHeight="true" ht="25.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -513,19 +513,19 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>세종특별자치시</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>12,954</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="19" customHeight="true" ht="25.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -535,19 +535,19 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>강원도</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>4,408</t>
+          <t>1,616</t>
         </is>
       </c>
     </row>
     <row r="20" customHeight="true" ht="25.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -557,19 +557,19 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>충청북도</t>
+          <t>강원도</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>2,192</t>
+          <t>3,115</t>
         </is>
       </c>
     </row>
     <row r="21" customHeight="true" ht="25.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -579,19 +579,19 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>충청남도</t>
+          <t>충청북도</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>3,814</t>
+          <t>273</t>
         </is>
       </c>
     </row>
     <row r="22" customHeight="true" ht="25.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>세종특별자치시</t>
+          <t>충청남도</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>2,510</t>
         </is>
       </c>
     </row>
     <row r="23" customHeight="true" ht="25.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -628,14 +628,14 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>2,743</t>
+          <t>661</t>
         </is>
       </c>
     </row>
     <row r="24" customHeight="true" ht="25.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -650,14 +650,14 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>3,598</t>
+          <t>1,059</t>
         </is>
       </c>
     </row>
     <row r="25" customHeight="true" ht="25.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -672,14 +672,14 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>6,987</t>
+          <t>2,154</t>
         </is>
       </c>
     </row>
     <row r="26" customHeight="true" ht="25.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -694,14 +694,14 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>5,347</t>
+          <t>3,617</t>
         </is>
       </c>
     </row>
     <row r="27" customHeight="true" ht="25.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -716,14 +716,14 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>2,807</t>
+          <t>1,095</t>
         </is>
       </c>
     </row>
     <row r="28" customHeight="true" ht="25.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -738,14 +738,14 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>16,997</t>
+          <t>2,131</t>
         </is>
       </c>
     </row>
     <row r="29" customHeight="true" ht="25.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -760,14 +760,14 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>53,176</t>
+          <t>16,874</t>
         </is>
       </c>
     </row>
     <row r="30" customHeight="true" ht="25.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -782,14 +782,14 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>70,173</t>
+          <t>19,005</t>
         </is>
       </c>
     </row>
     <row r="31" customHeight="true" ht="25.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -799,19 +799,19 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>40㎡이하</t>
+          <t>60㎡이하</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>2,160</t>
+          <t>4,640</t>
         </is>
       </c>
     </row>
     <row r="32" customHeight="true" ht="25.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -821,19 +821,19 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>40-60㎡</t>
+          <t>60-85㎡</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>7,197</t>
+          <t>13,665</t>
         </is>
       </c>
     </row>
     <row r="33" customHeight="true" ht="25.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -843,32 +843,2562 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>60-85㎡</t>
+          <t>85㎡초과</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>50,468</t>
+          <t>700</t>
         </is>
       </c>
     </row>
     <row r="34" customHeight="true" ht="25.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>계</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>17,710</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" customHeight="true" ht="25.0">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>민간부문</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>17,710</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" customHeight="true" ht="25.0">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>공공부문</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" customHeight="true" ht="25.0">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>(준공후)</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>7,449</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" customHeight="true" ht="25.0">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>전국</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>17,710</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" customHeight="true" ht="25.0">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>서울특별시</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" customHeight="true" ht="25.0">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>부산광역시</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" customHeight="true" ht="25.0">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>대구광역시</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>1,977</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" customHeight="true" ht="25.0">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>인천광역시</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" customHeight="true" ht="25.0">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>광주광역시</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" customHeight="true" ht="25.0">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>대전광역시</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" customHeight="true" ht="25.0">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>울산광역시</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" customHeight="true" ht="25.0">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>1,030</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" customHeight="true" ht="25.0">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>강원도</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>1,648</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" customHeight="true" ht="25.0">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>충청북도</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" customHeight="true" ht="25.0">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>충청남도</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>1,012</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" customHeight="true" ht="25.0">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>세종특별자치시</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" customHeight="true" ht="25.0">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>전라북도</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" customHeight="true" ht="25.0">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>전라남도</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>2,163</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" customHeight="true" ht="25.0">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>경상북도</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>4,386</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" customHeight="true" ht="25.0">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>경상남도</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>1,879</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" customHeight="true" ht="25.0">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>제주도</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" customHeight="true" ht="25.0">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>1,509</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" customHeight="true" ht="25.0">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>지방</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>16,201</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" customHeight="true" ht="25.0">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>계</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>17,710</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" customHeight="true" ht="25.0">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>40㎡이하</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>1,710</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" customHeight="true" ht="25.0">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>40-60㎡</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>2,479</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" customHeight="true" ht="25.0">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>60-85㎡</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>12,502</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" customHeight="true" ht="25.0">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>85㎡초과</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>1,019</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" customHeight="true" ht="25.0">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>계</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>68,107</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" customHeight="true" ht="25.0">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>민간부문</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>68,107</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" customHeight="true" ht="25.0">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>공공부문</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" customHeight="true" ht="25.0">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>(준공후)</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>7,518</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" customHeight="true" ht="25.0">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>전국</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>68,107</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" customHeight="true" ht="25.0">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>서울특별시</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" customHeight="true" ht="25.0">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>부산광역시</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>2,640</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" customHeight="true" ht="25.0">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>대구광역시</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>13,445</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" customHeight="true" ht="25.0">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>인천광역시</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>2,494</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" customHeight="true" ht="25.0">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>광주광역시</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" customHeight="true" ht="25.0">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>대전광역시</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>3,239</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" customHeight="true" ht="25.0">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>울산광역시</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>3,570</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" customHeight="true" ht="25.0">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>7,588</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" customHeight="true" ht="25.0">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>강원도</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>2,648</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" customHeight="true" ht="25.0">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>충청북도</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>3,225</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" customHeight="true" ht="25.0">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>충청남도</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>8,509</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" customHeight="true" ht="25.0">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>세종특별자치시</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" customHeight="true" ht="25.0">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>전라북도</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>2,520</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" customHeight="true" ht="25.0">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>전라남도</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>3,029</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" customHeight="true" ht="25.0">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>경상북도</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>7,674</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" customHeight="true" ht="25.0">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>경상남도</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" customHeight="true" ht="25.0">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>제주도</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>1,676</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" customHeight="true" ht="25.0">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>11,035</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" customHeight="true" ht="25.0">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>지방</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>57,072</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" customHeight="true" ht="25.0">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>계</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>68,107</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" customHeight="true" ht="25.0">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>40㎡이하</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>2,421</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" customHeight="true" ht="25.0">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>40-60㎡</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>8,005</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" customHeight="true" ht="25.0">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>60-85㎡</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>50,589</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" customHeight="true" ht="25.0">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>85㎡초과</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>7,092</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" customHeight="true" ht="25.0">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>계</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>62,489</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" customHeight="true" ht="25.0">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>민간부문</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>62,489</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" customHeight="true" ht="25.0">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>공공부문</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" customHeight="true" ht="25.0">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>(준공후)</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>10,857</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" customHeight="true" ht="25.0">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>전국</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>62,489</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" customHeight="true" ht="25.0">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>서울특별시</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>958</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" customHeight="true" ht="25.0">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>부산광역시</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>2,997</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" customHeight="true" ht="25.0">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>대구광역시</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>10,245</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" customHeight="true" ht="25.0">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>인천광역시</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>3,270</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" customHeight="true" ht="25.0">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>광주광역시</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" customHeight="true" ht="25.0">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>대전광역시</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" customHeight="true" ht="25.0">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>울산광역시</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>2,941</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" customHeight="true" ht="25.0">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>5,803</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" customHeight="true" ht="25.0">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>강원도</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>4,001</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" customHeight="true" ht="25.0">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>충청북도</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>3,442</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" customHeight="true" ht="25.0">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>충청남도</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>5,484</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" customHeight="true" ht="25.0">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>세종특별자치시</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" customHeight="true" ht="25.0">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>전라북도</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>3,075</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" customHeight="true" ht="25.0">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>전라남도</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>3,618</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" customHeight="true" ht="25.0">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>경상북도</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>8,862</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" customHeight="true" ht="25.0">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>경상남도</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>3,682</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" customHeight="true" ht="25.0">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>제주도</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>2,499</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" customHeight="true" ht="25.0">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>10,031</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" customHeight="true" ht="25.0">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>지방</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>52,458</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" customHeight="true" ht="25.0">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>계</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>62,489</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" customHeight="true" ht="25.0">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>40㎡이하</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>2,228</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" customHeight="true" ht="25.0">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>40-60㎡</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>7,199</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" customHeight="true" ht="25.0">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>60-85㎡</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>44,429</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" customHeight="true" ht="25.0">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>85㎡초과</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>8,633</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" customHeight="true" ht="25.0">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>계</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>70,173</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" customHeight="true" ht="25.0">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>민간부문</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>70,173</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" customHeight="true" ht="25.0">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>공공부문</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" customHeight="true" ht="25.0">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>부문별미분양현황</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>(준공후)</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>21,480</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" customHeight="true" ht="25.0">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>전국</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>70,173</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" customHeight="true" ht="25.0">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>서울특별시</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" customHeight="true" ht="25.0">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>부산광역시</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>4,720</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" customHeight="true" ht="25.0">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>대구광역시</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>8,807</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" customHeight="true" ht="25.0">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>인천광역시</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>3,086</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" customHeight="true" ht="25.0">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>광주광역시</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>1,242</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" customHeight="true" ht="25.0">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>대전광역시</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>2,319</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" customHeight="true" ht="25.0">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>울산광역시</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>4,131</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" customHeight="true" ht="25.0">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>12,954</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" customHeight="true" ht="25.0">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>강원도</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>4,408</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" customHeight="true" ht="25.0">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>충청북도</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>2,192</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" customHeight="true" ht="25.0">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>충청남도</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>3,814</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" customHeight="true" ht="25.0">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>세종특별자치시</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" customHeight="true" ht="25.0">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>전라북도</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>2,743</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" customHeight="true" ht="25.0">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>전라남도</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>3,598</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" customHeight="true" ht="25.0">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>경상북도</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>6,987</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" customHeight="true" ht="25.0">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>경상남도</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>5,347</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" customHeight="true" ht="25.0">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>제주도</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>2,807</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" customHeight="true" ht="25.0">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>16,997</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" customHeight="true" ht="25.0">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>시도별미분양현황</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>지방</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>53,176</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" customHeight="true" ht="25.0">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
         <is>
           <t>규모별미분양현황</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>계</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>70,173</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" customHeight="true" ht="25.0">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>40㎡이하</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>2,160</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" customHeight="true" ht="25.0">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>40-60㎡</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>7,197</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" customHeight="true" ht="25.0">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>60-85㎡</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>50,468</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" customHeight="true" ht="25.0">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>규모별미분양현황</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
         <is>
           <t>85㎡초과</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D149" s="6" t="inlineStr">
         <is>
           <t>10,348</t>
         </is>
@@ -879,10 +3409,26 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A6:A34"/>
+    <mergeCell ref="A6:A33"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="B10:B29"/>
-    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A34:A62"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B38:B57"/>
+    <mergeCell ref="B58:B62"/>
+    <mergeCell ref="A63:A91"/>
+    <mergeCell ref="B63:B66"/>
+    <mergeCell ref="B67:B86"/>
+    <mergeCell ref="B87:B91"/>
+    <mergeCell ref="A92:A120"/>
+    <mergeCell ref="B92:B95"/>
+    <mergeCell ref="B96:B115"/>
+    <mergeCell ref="B116:B120"/>
+    <mergeCell ref="A121:A149"/>
+    <mergeCell ref="B121:B124"/>
+    <mergeCell ref="B125:B144"/>
+    <mergeCell ref="B145:B149"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup blackAndWhite="false" orientation="portrait" paperSize="0" fitToWidth="0" fitToHeight="0"/>
